--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3B5EAB-931E-4B0B-8F40-19D200D5B054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01969708-39B5-4029-A6DB-2B81388F0BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
+    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="329">
   <si>
     <t>StepNo</t>
   </si>
@@ -1020,6 +1020,12 @@
   </si>
   <si>
     <t>Login password</t>
+  </si>
+  <si>
+    <t>Click Find record to open the patient search form</t>
+  </si>
+  <si>
+    <t>lnkTaskPanePatient</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F102DB-E514-4CAD-9E24-F8C5C238B897}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -1547,13 +1553,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>327</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1561,19 +1570,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1581,16 +1584,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1598,13 +1604,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
       </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1612,16 +1621,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1629,13 +1635,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1643,19 +1652,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1663,19 +1666,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
-      <c r="J14" t="s">
-        <v>32</v>
+      <c r="K14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1683,19 +1686,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
       </c>
-      <c r="K15" t="s">
-        <v>47</v>
+      <c r="J15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1703,16 +1706,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1720,13 +1726,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
       </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1734,16 +1743,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1751,19 +1757,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1771,19 +1774,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1791,19 +1794,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1811,19 +1814,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
         <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1831,19 +1834,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1851,16 +1854,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1868,13 +1874,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1882,19 +1891,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>40</v>
       </c>
-      <c r="D26" t="s">
-        <v>72</v>
-      </c>
       <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="K26" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1902,19 +1905,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
         <v>57</v>
       </c>
       <c r="K27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1922,19 +1925,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
       </c>
       <c r="K28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1942,19 +1945,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>57</v>
       </c>
       <c r="K29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1962,19 +1965,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
         <v>57</v>
       </c>
       <c r="K30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1982,19 +1985,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s">
         <v>57</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2002,16 +2005,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K32" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,13 +2025,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,19 +2042,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
         <v>92</v>
       </c>
-      <c r="D34" t="s">
-        <v>94</v>
-      </c>
       <c r="F34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2053,7 +2056,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
         <v>92</v>
@@ -2062,13 +2065,10 @@
         <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
-      </c>
-      <c r="G35" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" t="s">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="J35" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,16 +2076,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
         <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>98</v>
+      </c>
+      <c r="G36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2093,13 +2099,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2107,16 +2116,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2124,13 +2130,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>105</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2138,19 +2147,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
         <v>29</v>
       </c>
-      <c r="D40" t="s">
-        <v>30</v>
-      </c>
       <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2158,16 +2161,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
         <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2175,13 +2181,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
       </c>
+      <c r="D42" t="s">
+        <v>34</v>
+      </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,16 +2198,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2206,13 +2212,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
+        <v>110</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2220,25 +2229,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
       <c r="F45" t="s">
-        <v>98</v>
-      </c>
-      <c r="G45" t="s">
-        <v>115</v>
-      </c>
-      <c r="H45" t="s">
-        <v>116</v>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2246,7 +2243,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
         <v>112</v>
@@ -2255,10 +2252,16 @@
         <v>114</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
-      </c>
-      <c r="J46" t="s">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="G46" t="s">
+        <v>115</v>
+      </c>
+      <c r="H46" t="s">
+        <v>116</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2266,13 +2269,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
       </c>
       <c r="F47" t="s">
-        <v>120</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="J47" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2280,16 +2289,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2297,13 +2303,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
         <v>112</v>
       </c>
+      <c r="D49" t="s">
+        <v>122</v>
+      </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2311,16 +2320,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
         <v>112</v>
       </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2328,13 +2334,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>112</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2342,19 +2351,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
         <v>127</v>
       </c>
-      <c r="D52" t="s">
-        <v>129</v>
-      </c>
       <c r="F52" t="s">
-        <v>57</v>
-      </c>
-      <c r="K52" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2362,19 +2365,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
         <v>127</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F53" t="s">
         <v>57</v>
       </c>
       <c r="K53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2382,19 +2385,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
         <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
         <v>57</v>
       </c>
       <c r="K54" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2402,19 +2405,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
         <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F55" t="s">
         <v>57</v>
       </c>
       <c r="K55" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2422,16 +2425,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
         <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K56" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2439,13 +2445,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="D57" t="s">
+        <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2453,25 +2462,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D58" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="F58" t="s">
-        <v>98</v>
-      </c>
-      <c r="G58" t="s">
-        <v>115</v>
-      </c>
-      <c r="H58" t="s">
-        <v>116</v>
-      </c>
-      <c r="J58" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2479,12 +2476,24 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="C59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>51</v>
       </c>
       <c r="F59" t="s">
-        <v>120</v>
-      </c>
-      <c r="J59">
+        <v>98</v>
+      </c>
+      <c r="G59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" t="s">
+        <v>116</v>
+      </c>
+      <c r="J59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2493,16 +2502,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2510,13 +2516,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
         <v>144</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -2527,13 +2533,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>144</v>
+      </c>
+      <c r="D62" t="s">
+        <v>148</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2541,19 +2550,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
         <v>150</v>
       </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
       <c r="F63" t="s">
-        <v>57</v>
-      </c>
-      <c r="K63" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2561,19 +2564,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
         <v>150</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F64" t="s">
         <v>57</v>
       </c>
       <c r="K64" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2581,19 +2584,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s">
         <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F65" t="s">
         <v>57</v>
       </c>
       <c r="K65" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2601,19 +2604,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
         <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F66" t="s">
         <v>57</v>
       </c>
       <c r="K66" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2621,16 +2624,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C67" t="s">
         <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K67" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2638,13 +2644,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>165</v>
+        <v>150</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2652,16 +2661,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
         <v>165</v>
       </c>
-      <c r="D69" t="s">
-        <v>90</v>
-      </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2669,13 +2675,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
+        <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2683,25 +2692,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
         <v>112</v>
       </c>
-      <c r="D71" t="s">
-        <v>114</v>
-      </c>
       <c r="F71" t="s">
-        <v>98</v>
-      </c>
-      <c r="G71" t="s">
-        <v>115</v>
-      </c>
-      <c r="H71" t="s">
-        <v>116</v>
-      </c>
-      <c r="J71" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2709,12 +2706,24 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" t="s">
+        <v>114</v>
       </c>
       <c r="F72" t="s">
-        <v>120</v>
-      </c>
-      <c r="J72">
+        <v>98</v>
+      </c>
+      <c r="G72" t="s">
+        <v>115</v>
+      </c>
+      <c r="H72" t="s">
+        <v>116</v>
+      </c>
+      <c r="J72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2723,16 +2732,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
-      </c>
-      <c r="C73" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2740,13 +2746,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
         <v>112</v>
       </c>
+      <c r="D74" t="s">
+        <v>171</v>
+      </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2754,25 +2763,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
         <v>112</v>
       </c>
-      <c r="D75" t="s">
-        <v>171</v>
-      </c>
       <c r="F75" t="s">
-        <v>98</v>
-      </c>
-      <c r="G75" t="s">
-        <v>115</v>
-      </c>
-      <c r="H75" t="s">
-        <v>116</v>
-      </c>
-      <c r="J75" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2780,12 +2777,24 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>171</v>
       </c>
       <c r="F76" t="s">
-        <v>120</v>
-      </c>
-      <c r="J76">
+        <v>98</v>
+      </c>
+      <c r="G76" t="s">
+        <v>115</v>
+      </c>
+      <c r="H76" t="s">
+        <v>116</v>
+      </c>
+      <c r="J76" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2794,16 +2803,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
-      </c>
-      <c r="C77" t="s">
-        <v>144</v>
-      </c>
-      <c r="D77" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2811,13 +2817,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>144</v>
+      </c>
+      <c r="D78" t="s">
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2825,19 +2834,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
         <v>178</v>
       </c>
-      <c r="D79" t="s">
-        <v>180</v>
-      </c>
       <c r="F79" t="s">
-        <v>31</v>
-      </c>
-      <c r="K79" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2845,16 +2848,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C80" t="s">
         <v>178</v>
       </c>
       <c r="D80" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K80" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2862,13 +2868,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" t="s">
-        <v>185</v>
+        <v>178</v>
+      </c>
+      <c r="D81" t="s">
+        <v>183</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2876,19 +2885,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C82" t="s">
         <v>185</v>
       </c>
-      <c r="D82" t="s">
-        <v>187</v>
-      </c>
       <c r="F82" t="s">
-        <v>31</v>
-      </c>
-      <c r="K82" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2896,13 +2899,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
         <v>185</v>
       </c>
+      <c r="D83" t="s">
+        <v>187</v>
+      </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="K83" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2910,16 +2919,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C84" t="s">
         <v>185</v>
       </c>
-      <c r="D84" t="s">
-        <v>190</v>
-      </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2927,13 +2933,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C85" t="s">
         <v>185</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -2944,13 +2950,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C86" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="D86" t="s">
+        <v>192</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2958,16 +2967,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C87" t="s">
         <v>178</v>
       </c>
-      <c r="D87" t="s">
-        <v>90</v>
-      </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2975,13 +2981,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>178</v>
+      </c>
+      <c r="D88" t="s">
+        <v>90</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2989,13 +2998,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>197</v>
+        <v>195</v>
+      </c>
+      <c r="C89" t="s">
+        <v>196</v>
       </c>
       <c r="F89" t="s">
-        <v>120</v>
-      </c>
-      <c r="J89">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3003,19 +3012,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
-      </c>
-      <c r="C90" t="s">
-        <v>196</v>
-      </c>
-      <c r="D90" t="s">
-        <v>199</v>
-      </c>
-      <c r="E90" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F90" t="s">
-        <v>201</v>
+        <v>120</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -3023,13 +3026,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C91" t="s">
         <v>196</v>
       </c>
+      <c r="D91" t="s">
+        <v>199</v>
+      </c>
+      <c r="E91" t="s">
+        <v>200</v>
+      </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -3037,19 +3046,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C92" t="s">
         <v>196</v>
       </c>
-      <c r="D92" t="s">
-        <v>204</v>
-      </c>
-      <c r="E92" t="s">
-        <v>205</v>
-      </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3057,13 +3060,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C93" t="s">
         <v>196</v>
       </c>
+      <c r="D93" t="s">
+        <v>204</v>
+      </c>
+      <c r="E93" t="s">
+        <v>205</v>
+      </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3071,19 +3080,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
         <v>196</v>
       </c>
-      <c r="D94" t="s">
-        <v>208</v>
-      </c>
-      <c r="E94" t="s">
-        <v>205</v>
-      </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3091,13 +3094,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C95" t="s">
         <v>196</v>
       </c>
+      <c r="D95" t="s">
+        <v>208</v>
+      </c>
+      <c r="E95" t="s">
+        <v>205</v>
+      </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3105,19 +3114,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C96" t="s">
         <v>196</v>
       </c>
-      <c r="D96" t="s">
-        <v>211</v>
-      </c>
-      <c r="E96" t="s">
-        <v>205</v>
-      </c>
       <c r="F96" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -3125,13 +3128,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>196</v>
+      </c>
+      <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" t="s">
+        <v>205</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3139,16 +3148,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" t="s">
         <v>213</v>
       </c>
-      <c r="D98" t="s">
-        <v>215</v>
-      </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -3156,13 +3162,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
-        <v>196</v>
+        <v>213</v>
+      </c>
+      <c r="D99" t="s">
+        <v>215</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3170,28 +3179,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C100" t="s">
         <v>196</v>
       </c>
-      <c r="D100" t="s">
-        <v>199</v>
-      </c>
-      <c r="E100" t="s">
-        <v>200</v>
-      </c>
       <c r="F100" t="s">
-        <v>98</v>
-      </c>
-      <c r="G100" t="s">
-        <v>115</v>
-      </c>
-      <c r="H100" t="s">
-        <v>116</v>
-      </c>
-      <c r="J100" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -3199,12 +3193,27 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>217</v>
+      </c>
+      <c r="C101" t="s">
+        <v>196</v>
+      </c>
+      <c r="D101" t="s">
+        <v>199</v>
+      </c>
+      <c r="E101" t="s">
+        <v>200</v>
       </c>
       <c r="F101" t="s">
-        <v>120</v>
-      </c>
-      <c r="J101">
+        <v>98</v>
+      </c>
+      <c r="G101" t="s">
+        <v>115</v>
+      </c>
+      <c r="H101" t="s">
+        <v>116</v>
+      </c>
+      <c r="J101" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3213,19 +3222,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
-      </c>
-      <c r="C102" t="s">
-        <v>196</v>
-      </c>
-      <c r="D102" t="s">
-        <v>220</v>
-      </c>
-      <c r="E102" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F102" t="s">
-        <v>201</v>
+        <v>120</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -3233,13 +3236,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
         <v>196</v>
       </c>
+      <c r="D103" t="s">
+        <v>220</v>
+      </c>
+      <c r="E103" t="s">
+        <v>221</v>
+      </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3247,19 +3256,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s">
         <v>196</v>
       </c>
-      <c r="D104" t="s">
-        <v>224</v>
-      </c>
-      <c r="E104" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -3267,13 +3270,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C105" t="s">
         <v>196</v>
       </c>
+      <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
+        <v>225</v>
+      </c>
       <c r="F105" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -3281,19 +3290,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
         <v>196</v>
       </c>
-      <c r="D106" t="s">
-        <v>228</v>
-      </c>
-      <c r="E106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -3301,13 +3304,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C107" t="s">
         <v>196</v>
       </c>
+      <c r="D107" t="s">
+        <v>228</v>
+      </c>
+      <c r="E107" t="s">
+        <v>225</v>
+      </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -3315,19 +3324,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C108" t="s">
         <v>196</v>
       </c>
-      <c r="D108" t="s">
-        <v>231</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
-      </c>
       <c r="F108" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -3335,13 +3338,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C109" t="s">
-        <v>233</v>
+        <v>196</v>
+      </c>
+      <c r="D109" t="s">
+        <v>231</v>
+      </c>
+      <c r="E109" t="s">
+        <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -3349,16 +3358,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C110" t="s">
         <v>233</v>
       </c>
-      <c r="D110" t="s">
-        <v>215</v>
-      </c>
       <c r="F110" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -3366,13 +3372,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C111" t="s">
-        <v>196</v>
+        <v>233</v>
+      </c>
+      <c r="D111" t="s">
+        <v>215</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -3380,28 +3389,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C112" t="s">
         <v>196</v>
       </c>
-      <c r="D112" t="s">
-        <v>220</v>
-      </c>
-      <c r="E112" t="s">
-        <v>221</v>
-      </c>
       <c r="F112" t="s">
-        <v>98</v>
-      </c>
-      <c r="G112" t="s">
-        <v>115</v>
-      </c>
-      <c r="H112" t="s">
-        <v>116</v>
-      </c>
-      <c r="J112" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -3409,12 +3403,27 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>237</v>
+        <v>236</v>
+      </c>
+      <c r="C113" t="s">
+        <v>196</v>
+      </c>
+      <c r="D113" t="s">
+        <v>220</v>
+      </c>
+      <c r="E113" t="s">
+        <v>221</v>
       </c>
       <c r="F113" t="s">
-        <v>120</v>
-      </c>
-      <c r="J113">
+        <v>98</v>
+      </c>
+      <c r="G113" t="s">
+        <v>115</v>
+      </c>
+      <c r="H113" t="s">
+        <v>116</v>
+      </c>
+      <c r="J113" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3423,19 +3432,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
-      </c>
-      <c r="C114" t="s">
-        <v>196</v>
-      </c>
-      <c r="D114" t="s">
-        <v>239</v>
-      </c>
-      <c r="E114" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F114" t="s">
-        <v>201</v>
+        <v>120</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -3443,13 +3446,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C115" t="s">
         <v>196</v>
       </c>
+      <c r="D115" t="s">
+        <v>239</v>
+      </c>
+      <c r="E115" t="s">
+        <v>240</v>
+      </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -3457,19 +3466,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C116" t="s">
         <v>196</v>
       </c>
-      <c r="D116" t="s">
-        <v>243</v>
-      </c>
-      <c r="E116" t="s">
-        <v>244</v>
-      </c>
       <c r="F116" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -3477,13 +3480,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C117" t="s">
         <v>196</v>
       </c>
+      <c r="D117" t="s">
+        <v>243</v>
+      </c>
+      <c r="E117" t="s">
+        <v>244</v>
+      </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -3491,19 +3500,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C118" t="s">
         <v>196</v>
       </c>
-      <c r="D118" t="s">
-        <v>247</v>
-      </c>
-      <c r="E118" t="s">
-        <v>244</v>
-      </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -3511,13 +3514,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C119" t="s">
         <v>196</v>
       </c>
+      <c r="D119" t="s">
+        <v>247</v>
+      </c>
+      <c r="E119" t="s">
+        <v>244</v>
+      </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -3525,19 +3534,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C120" t="s">
         <v>196</v>
       </c>
-      <c r="D120" t="s">
-        <v>250</v>
-      </c>
-      <c r="E120" t="s">
-        <v>244</v>
-      </c>
       <c r="F120" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -3545,13 +3548,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C121" t="s">
-        <v>252</v>
+        <v>196</v>
+      </c>
+      <c r="D121" t="s">
+        <v>250</v>
+      </c>
+      <c r="E121" t="s">
+        <v>244</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -3559,16 +3568,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C122" t="s">
         <v>252</v>
       </c>
-      <c r="D122" t="s">
-        <v>90</v>
-      </c>
       <c r="F122" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -3576,13 +3582,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>196</v>
+        <v>252</v>
+      </c>
+      <c r="D123" t="s">
+        <v>90</v>
       </c>
       <c r="F123" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -3590,28 +3599,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C124" t="s">
         <v>196</v>
       </c>
-      <c r="D124" t="s">
-        <v>239</v>
-      </c>
-      <c r="E124" t="s">
-        <v>240</v>
-      </c>
       <c r="F124" t="s">
-        <v>98</v>
-      </c>
-      <c r="G124" t="s">
-        <v>115</v>
-      </c>
-      <c r="H124" t="s">
-        <v>116</v>
-      </c>
-      <c r="J124" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,12 +3613,27 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="C125" t="s">
+        <v>196</v>
+      </c>
+      <c r="D125" t="s">
+        <v>239</v>
+      </c>
+      <c r="E125" t="s">
+        <v>240</v>
       </c>
       <c r="F125" t="s">
-        <v>120</v>
-      </c>
-      <c r="J125">
+        <v>98</v>
+      </c>
+      <c r="G125" t="s">
+        <v>115</v>
+      </c>
+      <c r="H125" t="s">
+        <v>116</v>
+      </c>
+      <c r="J125" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3633,16 +3642,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>257</v>
-      </c>
-      <c r="C126" t="s">
-        <v>19</v>
-      </c>
-      <c r="D126" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F126" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -3650,13 +3656,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
       </c>
       <c r="D127" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F127" t="s">
         <v>23</v>
@@ -3667,12 +3673,29 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>259</v>
+      </c>
+      <c r="C128" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" t="s">
+        <v>260</v>
+      </c>
+      <c r="F128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
         <v>261</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C129" t="s">
         <v>15</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F129" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4092,4 +4115,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01969708-39B5-4029-A6DB-2B81388F0BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC71DF9E-75B2-4458-AC8B-180D566419D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="330">
   <si>
     <t>StepNo</t>
   </si>
@@ -1026,6 +1026,9 @@
   </si>
   <si>
     <t>lnkTaskPanePatient</t>
+  </si>
+  <si>
+    <t>pageSearchPatient</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1610,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC71DF9E-75B2-4458-AC8B-180D566419D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD821AEE-D9AD-4785-AD80-C158907A4272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="330">
   <si>
     <t>StepNo</t>
   </si>
@@ -185,15 +185,9 @@
     <t>POSTALCODE</t>
   </si>
   <si>
-    <t>Click Find to resolve address from postal code</t>
-  </si>
-  <si>
     <t>Wait for address lookup results</t>
   </si>
   <si>
-    <t>Select address row from lookup results</t>
-  </si>
-  <si>
     <t>tbl_SelectRow</t>
   </si>
   <si>
@@ -1029,6 +1023,12 @@
   </si>
   <si>
     <t>pageSearchPatient</t>
+  </si>
+  <si>
+    <t>// Click Find to resolve address from postal code</t>
+  </si>
+  <si>
+    <t>// Select address row from lookup results</t>
   </si>
 </sst>
 </file>
@@ -1556,13 +1556,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -1610,7 +1610,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
@@ -1729,7 +1729,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
@@ -1746,7 +1746,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
@@ -1760,13 +1760,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>329</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
         <v>23</v>
@@ -1777,19 +1777,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
         <v>31</v>
       </c>
+      <c r="J20" t="s">
+        <v>262</v>
+      </c>
       <c r="K20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1797,19 +1800,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" t="s">
         <v>56</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1817,19 +1820,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
         <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1837,19 +1840,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
       </c>
       <c r="K23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1857,19 +1860,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
         <v>31</v>
       </c>
       <c r="K24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1877,13 +1880,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s">
         <v>23</v>
@@ -1894,7 +1897,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
         <v>40</v>
@@ -1908,19 +1911,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1928,19 +1931,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1948,19 +1951,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1968,19 +1971,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1988,19 +1991,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2008,19 +2011,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2028,13 +2031,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
         <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>23</v>
@@ -2045,10 +2048,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
         <v>20</v>
@@ -2059,19 +2062,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" t="s">
         <v>93</v>
       </c>
-      <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="J35" t="s">
         <v>94</v>
-      </c>
-      <c r="F35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2079,22 +2082,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" t="s">
         <v>97</v>
       </c>
-      <c r="C36" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>98</v>
-      </c>
-      <c r="G36" t="s">
-        <v>99</v>
-      </c>
-      <c r="H36" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2102,13 +2105,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>23</v>
@@ -2119,7 +2122,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
@@ -2133,13 +2136,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F39" t="s">
         <v>23</v>
@@ -2150,7 +2153,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
         <v>29</v>
@@ -2164,7 +2167,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
         <v>29</v>
@@ -2215,13 +2218,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" t="s">
         <v>108</v>
-      </c>
-      <c r="C44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" t="s">
-        <v>110</v>
       </c>
       <c r="F44" t="s">
         <v>23</v>
@@ -2232,10 +2235,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -2246,22 +2249,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46" t="s">
         <v>113</v>
       </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="H46" t="s">
         <v>114</v>
-      </c>
-      <c r="F46" t="s">
-        <v>98</v>
-      </c>
-      <c r="G46" t="s">
-        <v>115</v>
-      </c>
-      <c r="H46" t="s">
-        <v>116</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2272,19 +2275,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" t="s">
         <v>112</v>
       </c>
-      <c r="D47" t="s">
-        <v>114</v>
-      </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2292,10 +2295,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2306,13 +2309,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
         <v>23</v>
@@ -2323,10 +2326,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
         <v>20</v>
@@ -2337,13 +2340,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F51" t="s">
         <v>23</v>
@@ -2354,10 +2357,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F52" t="s">
         <v>20</v>
@@ -2368,19 +2371,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" t="s">
+        <v>55</v>
+      </c>
+      <c r="K53" t="s">
         <v>128</v>
-      </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
-        <v>129</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
-      <c r="K53" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2388,19 +2391,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
+        <v>130</v>
+      </c>
+      <c r="F54" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" t="s">
         <v>131</v>
-      </c>
-      <c r="C54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" t="s">
-        <v>57</v>
-      </c>
-      <c r="K54" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2408,19 +2411,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>132</v>
+      </c>
+      <c r="C55" t="s">
+        <v>125</v>
+      </c>
+      <c r="D55" t="s">
+        <v>133</v>
+      </c>
+      <c r="F55" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" t="s">
         <v>134</v>
-      </c>
-      <c r="C55" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" t="s">
-        <v>135</v>
-      </c>
-      <c r="F55" t="s">
-        <v>57</v>
-      </c>
-      <c r="K55" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2428,19 +2431,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" t="s">
+        <v>136</v>
+      </c>
+      <c r="F56" t="s">
+        <v>55</v>
+      </c>
+      <c r="K56" t="s">
         <v>137</v>
-      </c>
-      <c r="C56" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" t="s">
-        <v>138</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-      <c r="K56" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2448,13 +2451,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F57" t="s">
         <v>23</v>
@@ -2465,10 +2468,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F58" t="s">
         <v>20</v>
@@ -2479,22 +2482,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G59" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
@@ -2505,10 +2508,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2519,13 +2522,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -2536,13 +2539,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F62" t="s">
         <v>23</v>
@@ -2553,10 +2556,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F63" t="s">
         <v>20</v>
@@ -2567,19 +2570,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" t="s">
+        <v>55</v>
+      </c>
+      <c r="K64" t="s">
         <v>151</v>
-      </c>
-      <c r="C64" t="s">
-        <v>150</v>
-      </c>
-      <c r="D64" t="s">
-        <v>152</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2587,19 +2590,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" t="s">
+        <v>55</v>
+      </c>
+      <c r="K65" t="s">
         <v>154</v>
-      </c>
-      <c r="C65" t="s">
-        <v>150</v>
-      </c>
-      <c r="D65" t="s">
-        <v>155</v>
-      </c>
-      <c r="F65" t="s">
-        <v>57</v>
-      </c>
-      <c r="K65" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2607,19 +2610,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>155</v>
+      </c>
+      <c r="C66" t="s">
+        <v>148</v>
+      </c>
+      <c r="D66" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" t="s">
+        <v>55</v>
+      </c>
+      <c r="K66" t="s">
         <v>157</v>
-      </c>
-      <c r="C66" t="s">
-        <v>150</v>
-      </c>
-      <c r="D66" t="s">
-        <v>158</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-      <c r="K66" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2627,19 +2630,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" t="s">
+        <v>55</v>
+      </c>
+      <c r="K67" t="s">
         <v>160</v>
-      </c>
-      <c r="C67" t="s">
-        <v>150</v>
-      </c>
-      <c r="D67" t="s">
-        <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>57</v>
-      </c>
-      <c r="K67" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2647,13 +2650,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F68" t="s">
         <v>23</v>
@@ -2664,10 +2667,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F69" t="s">
         <v>20</v>
@@ -2678,13 +2681,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D70" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F70" t="s">
         <v>23</v>
@@ -2695,10 +2698,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F71" t="s">
         <v>20</v>
@@ -2709,22 +2712,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" t="s">
         <v>112</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
+        <v>96</v>
+      </c>
+      <c r="G72" t="s">
+        <v>113</v>
+      </c>
+      <c r="H72" t="s">
         <v>114</v>
-      </c>
-      <c r="F72" t="s">
-        <v>98</v>
-      </c>
-      <c r="G72" t="s">
-        <v>115</v>
-      </c>
-      <c r="H72" t="s">
-        <v>116</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -2735,10 +2738,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F73" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2749,13 +2752,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
@@ -2766,10 +2769,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F75" t="s">
         <v>20</v>
@@ -2780,22 +2783,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G76" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H76" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
@@ -2806,10 +2809,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2820,13 +2823,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -2837,10 +2840,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F79" t="s">
         <v>20</v>
@@ -2851,19 +2854,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D80" t="s">
         <v>178</v>
-      </c>
-      <c r="D80" t="s">
-        <v>180</v>
       </c>
       <c r="F80" t="s">
         <v>31</v>
       </c>
       <c r="K80" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2871,13 +2874,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
@@ -2888,10 +2891,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
         <v>20</v>
@@ -2902,19 +2905,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C83" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" t="s">
         <v>185</v>
-      </c>
-      <c r="D83" t="s">
-        <v>187</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
       </c>
       <c r="K83" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2922,10 +2925,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -2936,13 +2939,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -2953,13 +2956,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C86" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
@@ -2970,10 +2973,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F87" t="s">
         <v>20</v>
@@ -2984,13 +2987,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C88" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
@@ -3001,10 +3004,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F89" t="s">
         <v>20</v>
@@ -3015,10 +3018,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3029,19 +3032,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>196</v>
+      </c>
+      <c r="C91" t="s">
+        <v>194</v>
+      </c>
+      <c r="D91" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" t="s">
         <v>198</v>
       </c>
-      <c r="C91" t="s">
-        <v>196</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>199</v>
-      </c>
-      <c r="E91" t="s">
-        <v>200</v>
-      </c>
-      <c r="F91" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,10 +3052,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C92" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F92" t="s">
         <v>20</v>
@@ -3063,16 +3066,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" t="s">
+        <v>194</v>
+      </c>
+      <c r="D93" t="s">
+        <v>202</v>
+      </c>
+      <c r="E93" t="s">
         <v>203</v>
-      </c>
-      <c r="C93" t="s">
-        <v>196</v>
-      </c>
-      <c r="D93" t="s">
-        <v>204</v>
-      </c>
-      <c r="E93" t="s">
-        <v>205</v>
       </c>
       <c r="F93" t="s">
         <v>23</v>
@@ -3083,10 +3086,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F94" t="s">
         <v>20</v>
@@ -3097,16 +3100,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D95" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -3117,10 +3120,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C96" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F96" t="s">
         <v>20</v>
@@ -3131,16 +3134,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C97" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s">
         <v>23</v>
@@ -3151,10 +3154,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C98" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F98" t="s">
         <v>20</v>
@@ -3165,13 +3168,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C99" t="s">
+        <v>211</v>
+      </c>
+      <c r="D99" t="s">
         <v>213</v>
-      </c>
-      <c r="D99" t="s">
-        <v>215</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
@@ -3182,10 +3185,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C100" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
@@ -3196,25 +3199,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D101" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E101" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F101" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G101" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
@@ -3225,10 +3228,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F102" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3239,19 +3242,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" t="s">
+        <v>194</v>
+      </c>
+      <c r="D103" t="s">
+        <v>218</v>
+      </c>
+      <c r="E103" t="s">
         <v>219</v>
       </c>
-      <c r="C103" t="s">
-        <v>196</v>
-      </c>
-      <c r="D103" t="s">
-        <v>220</v>
-      </c>
-      <c r="E103" t="s">
-        <v>221</v>
-      </c>
       <c r="F103" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3259,10 +3262,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C104" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -3273,16 +3276,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" t="s">
+        <v>194</v>
+      </c>
+      <c r="D105" t="s">
+        <v>222</v>
+      </c>
+      <c r="E105" t="s">
         <v>223</v>
-      </c>
-      <c r="C105" t="s">
-        <v>196</v>
-      </c>
-      <c r="D105" t="s">
-        <v>224</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
@@ -3293,10 +3296,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C106" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
@@ -3307,16 +3310,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C107" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
@@ -3327,10 +3330,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C108" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -3341,16 +3344,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C109" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D109" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F109" t="s">
         <v>23</v>
@@ -3361,10 +3364,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C110" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -3375,13 +3378,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C111" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D111" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F111" t="s">
         <v>23</v>
@@ -3392,10 +3395,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C112" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F112" t="s">
         <v>20</v>
@@ -3406,25 +3409,25 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D113" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E113" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F113" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H113" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
@@ -3435,10 +3438,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F114" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -3449,19 +3452,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
+        <v>236</v>
+      </c>
+      <c r="C115" t="s">
+        <v>194</v>
+      </c>
+      <c r="D115" t="s">
+        <v>237</v>
+      </c>
+      <c r="E115" t="s">
         <v>238</v>
       </c>
-      <c r="C115" t="s">
-        <v>196</v>
-      </c>
-      <c r="D115" t="s">
-        <v>239</v>
-      </c>
-      <c r="E115" t="s">
-        <v>240</v>
-      </c>
       <c r="F115" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -3469,10 +3472,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C116" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F116" t="s">
         <v>20</v>
@@ -3483,16 +3486,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>240</v>
+      </c>
+      <c r="C117" t="s">
+        <v>194</v>
+      </c>
+      <c r="D117" t="s">
+        <v>241</v>
+      </c>
+      <c r="E117" t="s">
         <v>242</v>
-      </c>
-      <c r="C117" t="s">
-        <v>196</v>
-      </c>
-      <c r="D117" t="s">
-        <v>243</v>
-      </c>
-      <c r="E117" t="s">
-        <v>244</v>
       </c>
       <c r="F117" t="s">
         <v>23</v>
@@ -3503,10 +3506,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C118" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
@@ -3517,16 +3520,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C119" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D119" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E119" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F119" t="s">
         <v>23</v>
@@ -3537,10 +3540,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C120" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -3551,16 +3554,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D121" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E121" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F121" t="s">
         <v>23</v>
@@ -3571,10 +3574,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C122" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F122" t="s">
         <v>20</v>
@@ -3585,13 +3588,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C123" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D123" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F123" t="s">
         <v>23</v>
@@ -3602,10 +3605,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C124" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
         <v>20</v>
@@ -3616,25 +3619,25 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C125" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D125" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E125" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F125" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G125" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H125" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
@@ -3645,10 +3648,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F126" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -3659,13 +3662,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
       </c>
       <c r="D127" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F127" t="s">
         <v>23</v>
@@ -3676,13 +3679,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C128" t="s">
         <v>19</v>
       </c>
       <c r="D128" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F128" t="s">
         <v>23</v>
@@ -3693,7 +3696,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C129" t="s">
         <v>15</v>
@@ -3744,78 +3747,78 @@
         <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" t="s">
         <v>262</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>263</v>
-      </c>
-      <c r="C2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" t="s">
-        <v>265</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3824,52 +3827,52 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J2" t="s">
         <v>266</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>267</v>
       </c>
-      <c r="I2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>268</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>269</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>270</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>271</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>272</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>273</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>274</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>275</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>276</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>277</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>278</v>
-      </c>
-      <c r="U2" t="s">
-        <v>279</v>
-      </c>
-      <c r="V2" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3888,94 +3891,94 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3983,7 +3986,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3991,47 +3994,47 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4051,13 +4054,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,54 +4068,54 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
         <v>322</v>
-      </c>
-      <c r="B5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD821AEE-D9AD-4785-AD80-C158907A4272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406EC438-B37F-412A-BA66-556A220BA6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="329">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1485,25 +1482,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1511,13 +1505,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,16 +1519,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1542,13 +1536,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1556,16 +1550,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>325</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>326</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1573,13 +1567,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>26</v>
-      </c>
-      <c r="J8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1587,19 +1581,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
         <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1607,16 +1601,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>327</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1624,13 +1618,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,16 +1632,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1655,13 +1649,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1669,19 +1663,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1689,19 +1683,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
         <v>30</v>
       </c>
-      <c r="F15" t="s">
+      <c r="J15" t="s">
         <v>31</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1709,19 +1703,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1729,16 +1723,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1746,13 +1740,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1760,16 +1754,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1777,22 +1771,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" t="s">
+        <v>261</v>
+      </c>
+      <c r="K20" t="s">
         <v>51</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" t="s">
-        <v>262</v>
-      </c>
-      <c r="K20" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1800,19 +1794,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
         <v>53</v>
       </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>54</v>
       </c>
-      <c r="F21" t="s">
+      <c r="K21" t="s">
         <v>55</v>
-      </c>
-      <c r="K21" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1820,19 +1814,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" t="s">
         <v>58</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1840,19 +1834,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
         <v>60</v>
       </c>
-      <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" t="s">
         <v>61</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1860,19 +1854,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
         <v>63</v>
       </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" t="s">
         <v>64</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1880,16 +1874,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
         <v>66</v>
       </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
-      </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1897,13 +1891,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1911,19 +1905,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" t="s">
         <v>70</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="K27" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1931,19 +1925,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
         <v>72</v>
       </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" t="s">
         <v>73</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="K28" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1951,19 +1945,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
         <v>75</v>
       </c>
-      <c r="C29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" t="s">
         <v>76</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="K29" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1971,19 +1965,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
         <v>78</v>
       </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" t="s">
         <v>79</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="K30" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1991,19 +1985,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
         <v>81</v>
       </c>
-      <c r="C31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K31" t="s">
         <v>82</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="K31" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2011,19 +2005,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
         <v>84</v>
       </c>
-      <c r="C32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K32" t="s">
         <v>85</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-      <c r="K32" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2031,16 +2025,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
         <v>87</v>
       </c>
-      <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" t="s">
-        <v>88</v>
-      </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2048,13 +2042,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
         <v>89</v>
       </c>
-      <c r="C34" t="s">
-        <v>90</v>
-      </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2062,19 +2056,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" t="s">
         <v>91</v>
       </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>92</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>93</v>
-      </c>
-      <c r="J35" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2082,22 +2076,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" t="s">
         <v>95</v>
       </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>96</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>97</v>
-      </c>
-      <c r="H36" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2105,16 +2099,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" t="s">
         <v>99</v>
       </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>100</v>
-      </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2122,13 +2116,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
         <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2136,16 +2130,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
         <v>102</v>
       </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" t="s">
-        <v>103</v>
-      </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2153,13 +2147,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2167,19 +2161,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
         <v>29</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>30</v>
       </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>31</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2187,16 +2181,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="C42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2204,13 +2198,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2218,16 +2212,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" t="s">
         <v>106</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>107</v>
       </c>
-      <c r="D44" t="s">
-        <v>108</v>
-      </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2235,13 +2229,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" t="s">
         <v>109</v>
       </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2249,22 +2243,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
         <v>111</v>
       </c>
-      <c r="C46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
+        <v>95</v>
+      </c>
+      <c r="G46" t="s">
         <v>112</v>
       </c>
-      <c r="F46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>113</v>
-      </c>
-      <c r="H46" t="s">
-        <v>114</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2275,19 +2269,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F47" t="s">
+        <v>92</v>
+      </c>
+      <c r="J47" t="s">
         <v>115</v>
-      </c>
-      <c r="C47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" t="s">
-        <v>93</v>
-      </c>
-      <c r="J47" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2295,10 +2289,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" t="s">
         <v>117</v>
-      </c>
-      <c r="F48" t="s">
-        <v>118</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2309,16 +2303,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" t="s">
         <v>119</v>
       </c>
-      <c r="C49" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" t="s">
-        <v>120</v>
-      </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2326,13 +2320,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2340,16 +2334,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" t="s">
         <v>122</v>
       </c>
-      <c r="C51" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" t="s">
-        <v>123</v>
-      </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2357,13 +2351,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" t="s">
         <v>124</v>
       </c>
-      <c r="C52" t="s">
-        <v>125</v>
-      </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2371,19 +2365,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" t="s">
         <v>126</v>
       </c>
-      <c r="C53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="K53" t="s">
         <v>127</v>
-      </c>
-      <c r="F53" t="s">
-        <v>55</v>
-      </c>
-      <c r="K53" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2391,19 +2385,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" t="s">
         <v>129</v>
       </c>
-      <c r="C54" t="s">
-        <v>125</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>54</v>
+      </c>
+      <c r="K54" t="s">
         <v>130</v>
-      </c>
-      <c r="F54" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2411,19 +2405,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s">
         <v>132</v>
       </c>
-      <c r="C55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
+        <v>54</v>
+      </c>
+      <c r="K55" t="s">
         <v>133</v>
-      </c>
-      <c r="F55" t="s">
-        <v>55</v>
-      </c>
-      <c r="K55" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2431,19 +2425,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" t="s">
         <v>135</v>
       </c>
-      <c r="C56" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" t="s">
         <v>136</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-      <c r="K56" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2451,16 +2445,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" t="s">
         <v>138</v>
       </c>
-      <c r="C57" t="s">
-        <v>125</v>
-      </c>
-      <c r="D57" t="s">
-        <v>139</v>
-      </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2468,13 +2462,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2482,22 +2476,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
         <v>141</v>
       </c>
-      <c r="C59" t="s">
-        <v>142</v>
-      </c>
       <c r="D59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G59" t="s">
+        <v>112</v>
+      </c>
+      <c r="H59" t="s">
         <v>113</v>
-      </c>
-      <c r="H59" t="s">
-        <v>114</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
@@ -2508,10 +2502,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2522,16 +2516,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2539,16 +2533,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" t="s">
         <v>145</v>
       </c>
-      <c r="C62" t="s">
-        <v>142</v>
-      </c>
-      <c r="D62" t="s">
-        <v>146</v>
-      </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2556,13 +2550,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" t="s">
         <v>147</v>
       </c>
-      <c r="C63" t="s">
-        <v>148</v>
-      </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2570,19 +2564,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" t="s">
         <v>149</v>
       </c>
-      <c r="C64" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K64" t="s">
         <v>150</v>
-      </c>
-      <c r="F64" t="s">
-        <v>55</v>
-      </c>
-      <c r="K64" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2590,19 +2584,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" t="s">
+        <v>147</v>
+      </c>
+      <c r="D65" t="s">
         <v>152</v>
       </c>
-      <c r="C65" t="s">
-        <v>148</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>54</v>
+      </c>
+      <c r="K65" t="s">
         <v>153</v>
-      </c>
-      <c r="F65" t="s">
-        <v>55</v>
-      </c>
-      <c r="K65" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2610,19 +2604,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" t="s">
         <v>155</v>
       </c>
-      <c r="C66" t="s">
-        <v>148</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="F66" t="s">
+        <v>54</v>
+      </c>
+      <c r="K66" t="s">
         <v>156</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-      <c r="K66" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2630,19 +2624,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" t="s">
         <v>158</v>
       </c>
-      <c r="C67" t="s">
-        <v>148</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="F67" t="s">
+        <v>54</v>
+      </c>
+      <c r="K67" t="s">
         <v>159</v>
-      </c>
-      <c r="F67" t="s">
-        <v>55</v>
-      </c>
-      <c r="K67" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2650,16 +2644,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2667,13 +2661,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" t="s">
         <v>162</v>
       </c>
-      <c r="C69" t="s">
-        <v>163</v>
-      </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2681,16 +2675,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2698,13 +2692,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2712,22 +2706,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D72" t="s">
+        <v>111</v>
+      </c>
+      <c r="F72" t="s">
+        <v>95</v>
+      </c>
+      <c r="G72" t="s">
         <v>112</v>
       </c>
-      <c r="F72" t="s">
-        <v>96</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>113</v>
-      </c>
-      <c r="H72" t="s">
-        <v>114</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -2738,10 +2732,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2752,16 +2746,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" t="s">
         <v>168</v>
       </c>
-      <c r="C74" t="s">
-        <v>110</v>
-      </c>
-      <c r="D74" t="s">
-        <v>169</v>
-      </c>
       <c r="F74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,13 +2763,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2783,22 +2777,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G76" t="s">
+        <v>112</v>
+      </c>
+      <c r="H76" t="s">
         <v>113</v>
-      </c>
-      <c r="H76" t="s">
-        <v>114</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
@@ -2809,10 +2803,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2823,16 +2817,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" t="s">
+        <v>141</v>
+      </c>
+      <c r="D78" t="s">
         <v>173</v>
       </c>
-      <c r="C78" t="s">
-        <v>142</v>
-      </c>
-      <c r="D78" t="s">
-        <v>174</v>
-      </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2840,13 +2834,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" t="s">
         <v>175</v>
       </c>
-      <c r="C79" t="s">
-        <v>176</v>
-      </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2854,19 +2848,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" t="s">
         <v>177</v>
       </c>
-      <c r="C80" t="s">
-        <v>176</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" t="s">
         <v>178</v>
-      </c>
-      <c r="F80" t="s">
-        <v>31</v>
-      </c>
-      <c r="K80" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,16 +2868,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" t="s">
+        <v>175</v>
+      </c>
+      <c r="D81" t="s">
         <v>180</v>
       </c>
-      <c r="C81" t="s">
-        <v>176</v>
-      </c>
-      <c r="D81" t="s">
-        <v>181</v>
-      </c>
       <c r="F81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2891,13 +2885,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" t="s">
         <v>182</v>
       </c>
-      <c r="C82" t="s">
-        <v>183</v>
-      </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2905,19 +2899,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>182</v>
+      </c>
+      <c r="D83" t="s">
         <v>184</v>
       </c>
-      <c r="C83" t="s">
-        <v>183</v>
-      </c>
-      <c r="D83" t="s">
-        <v>185</v>
-      </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2925,13 +2919,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C84" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2939,16 +2933,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>186</v>
+      </c>
+      <c r="C85" t="s">
+        <v>182</v>
+      </c>
+      <c r="D85" t="s">
         <v>187</v>
       </c>
-      <c r="C85" t="s">
-        <v>183</v>
-      </c>
-      <c r="D85" t="s">
-        <v>188</v>
-      </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2956,16 +2950,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" t="s">
+        <v>182</v>
+      </c>
+      <c r="D86" t="s">
         <v>189</v>
       </c>
-      <c r="C86" t="s">
-        <v>183</v>
-      </c>
-      <c r="D86" t="s">
-        <v>190</v>
-      </c>
       <c r="F86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2973,13 +2967,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2987,16 +2981,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -3004,13 +2998,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" t="s">
         <v>193</v>
       </c>
-      <c r="C89" t="s">
-        <v>194</v>
-      </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3018,10 +3012,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F90" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3032,19 +3026,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" t="s">
+        <v>193</v>
+      </c>
+      <c r="D91" t="s">
         <v>196</v>
       </c>
-      <c r="C91" t="s">
-        <v>194</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>197</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>198</v>
-      </c>
-      <c r="F91" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -3052,13 +3046,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3066,19 +3060,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" t="s">
+        <v>193</v>
+      </c>
+      <c r="D93" t="s">
         <v>201</v>
       </c>
-      <c r="C93" t="s">
-        <v>194</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>202</v>
       </c>
-      <c r="E93" t="s">
-        <v>203</v>
-      </c>
       <c r="F93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3086,13 +3080,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3100,19 +3094,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" t="s">
+        <v>193</v>
+      </c>
+      <c r="D95" t="s">
         <v>205</v>
       </c>
-      <c r="C95" t="s">
-        <v>194</v>
-      </c>
-      <c r="D95" t="s">
-        <v>206</v>
-      </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3120,13 +3114,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C96" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -3134,19 +3128,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>207</v>
+      </c>
+      <c r="C97" t="s">
+        <v>193</v>
+      </c>
+      <c r="D97" t="s">
         <v>208</v>
       </c>
-      <c r="C97" t="s">
-        <v>194</v>
-      </c>
-      <c r="D97" t="s">
-        <v>209</v>
-      </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3154,13 +3148,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>209</v>
+      </c>
+      <c r="C98" t="s">
         <v>210</v>
       </c>
-      <c r="C98" t="s">
-        <v>211</v>
-      </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -3168,16 +3162,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>211</v>
+      </c>
+      <c r="C99" t="s">
+        <v>210</v>
+      </c>
+      <c r="D99" t="s">
         <v>212</v>
       </c>
-      <c r="C99" t="s">
-        <v>211</v>
-      </c>
-      <c r="D99" t="s">
-        <v>213</v>
-      </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3185,13 +3179,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -3199,25 +3193,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D101" t="s">
+        <v>196</v>
+      </c>
+      <c r="E101" t="s">
         <v>197</v>
       </c>
-      <c r="E101" t="s">
-        <v>198</v>
-      </c>
       <c r="F101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G101" t="s">
+        <v>112</v>
+      </c>
+      <c r="H101" t="s">
         <v>113</v>
-      </c>
-      <c r="H101" t="s">
-        <v>114</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
@@ -3228,10 +3222,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3242,19 +3236,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>216</v>
+      </c>
+      <c r="C103" t="s">
+        <v>193</v>
+      </c>
+      <c r="D103" t="s">
         <v>217</v>
       </c>
-      <c r="C103" t="s">
-        <v>194</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>218</v>
       </c>
-      <c r="E103" t="s">
-        <v>219</v>
-      </c>
       <c r="F103" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3262,13 +3256,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C104" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -3276,19 +3270,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>220</v>
+      </c>
+      <c r="C105" t="s">
+        <v>193</v>
+      </c>
+      <c r="D105" t="s">
         <v>221</v>
       </c>
-      <c r="C105" t="s">
-        <v>194</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>222</v>
       </c>
-      <c r="E105" t="s">
-        <v>223</v>
-      </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -3296,13 +3290,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -3310,19 +3304,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>224</v>
+      </c>
+      <c r="C107" t="s">
+        <v>193</v>
+      </c>
+      <c r="D107" t="s">
         <v>225</v>
       </c>
-      <c r="C107" t="s">
-        <v>194</v>
-      </c>
-      <c r="D107" t="s">
-        <v>226</v>
-      </c>
       <c r="E107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -3330,13 +3324,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -3344,19 +3338,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>227</v>
+      </c>
+      <c r="C109" t="s">
+        <v>193</v>
+      </c>
+      <c r="D109" t="s">
         <v>228</v>
       </c>
-      <c r="C109" t="s">
-        <v>194</v>
-      </c>
-      <c r="D109" t="s">
-        <v>229</v>
-      </c>
       <c r="E109" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -3364,13 +3358,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>229</v>
+      </c>
+      <c r="C110" t="s">
         <v>230</v>
       </c>
-      <c r="C110" t="s">
-        <v>231</v>
-      </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -3378,16 +3372,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C111" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D111" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -3395,13 +3389,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C112" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -3409,25 +3403,25 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D113" t="s">
+        <v>217</v>
+      </c>
+      <c r="E113" t="s">
         <v>218</v>
       </c>
-      <c r="E113" t="s">
-        <v>219</v>
-      </c>
       <c r="F113" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G113" t="s">
+        <v>112</v>
+      </c>
+      <c r="H113" t="s">
         <v>113</v>
-      </c>
-      <c r="H113" t="s">
-        <v>114</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
@@ -3438,10 +3432,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -3452,19 +3446,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
+        <v>235</v>
+      </c>
+      <c r="C115" t="s">
+        <v>193</v>
+      </c>
+      <c r="D115" t="s">
         <v>236</v>
       </c>
-      <c r="C115" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>237</v>
       </c>
-      <c r="E115" t="s">
-        <v>238</v>
-      </c>
       <c r="F115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -3472,13 +3466,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -3486,19 +3480,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>239</v>
+      </c>
+      <c r="C117" t="s">
+        <v>193</v>
+      </c>
+      <c r="D117" t="s">
         <v>240</v>
       </c>
-      <c r="C117" t="s">
-        <v>194</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>241</v>
       </c>
-      <c r="E117" t="s">
-        <v>242</v>
-      </c>
       <c r="F117" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -3506,13 +3500,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F118" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -3520,19 +3514,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" t="s">
+        <v>193</v>
+      </c>
+      <c r="D119" t="s">
         <v>244</v>
       </c>
-      <c r="C119" t="s">
-        <v>194</v>
-      </c>
-      <c r="D119" t="s">
-        <v>245</v>
-      </c>
       <c r="E119" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -3540,13 +3534,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -3554,19 +3548,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>246</v>
+      </c>
+      <c r="C121" t="s">
+        <v>193</v>
+      </c>
+      <c r="D121" t="s">
         <v>247</v>
       </c>
-      <c r="C121" t="s">
-        <v>194</v>
-      </c>
-      <c r="D121" t="s">
-        <v>248</v>
-      </c>
       <c r="E121" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -3574,13 +3568,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>248</v>
+      </c>
+      <c r="C122" t="s">
         <v>249</v>
       </c>
-      <c r="C122" t="s">
-        <v>250</v>
-      </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -3588,16 +3582,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C123" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D123" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F123" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -3605,13 +3599,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C124" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,25 +3613,25 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C125" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D125" t="s">
+        <v>236</v>
+      </c>
+      <c r="E125" t="s">
         <v>237</v>
       </c>
-      <c r="E125" t="s">
-        <v>238</v>
-      </c>
       <c r="F125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G125" t="s">
+        <v>112</v>
+      </c>
+      <c r="H125" t="s">
         <v>113</v>
-      </c>
-      <c r="H125" t="s">
-        <v>114</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
@@ -3648,10 +3642,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F126" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -3662,16 +3656,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>254</v>
+      </c>
+      <c r="C127" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" t="s">
         <v>255</v>
       </c>
-      <c r="C127" t="s">
-        <v>19</v>
-      </c>
-      <c r="D127" t="s">
-        <v>256</v>
-      </c>
       <c r="F127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -3679,16 +3673,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" t="s">
         <v>257</v>
       </c>
-      <c r="C128" t="s">
-        <v>19</v>
-      </c>
-      <c r="D128" t="s">
-        <v>258</v>
-      </c>
       <c r="F128" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,13 +3690,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3741,84 +3735,84 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" t="s">
         <v>260</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>261</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>262</v>
-      </c>
-      <c r="D2" t="s">
-        <v>263</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3827,52 +3821,52 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" t="s">
         <v>264</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J2" t="s">
         <v>265</v>
       </c>
-      <c r="I2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>266</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>267</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>268</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>269</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>270</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>271</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>272</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>273</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>274</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>275</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>276</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>277</v>
-      </c>
-      <c r="V2" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3891,94 +3885,94 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3986,7 +3980,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3994,47 +3988,47 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>308</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4054,68 +4048,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" t="s">
         <v>315</v>
-      </c>
-      <c r="C2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" t="s">
         <v>317</v>
-      </c>
-      <c r="C3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" t="s">
         <v>320</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>321</v>
-      </c>
-      <c r="C5" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" t="s">
         <v>323</v>
       </c>
-      <c r="B6" t="s">
-        <v>324</v>
-      </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406EC438-B37F-412A-BA66-556A220BA6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803FEB36-CD08-43A3-9AFE-C9C7943B50EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="330">
   <si>
     <t>StepNo</t>
   </si>
@@ -1026,6 +1026,9 @@
   </si>
   <si>
     <t>// Select address row from lookup results</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1644,7 @@
         <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2034,7 +2037,7 @@
         <v>87</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2108,7 +2111,7 @@
         <v>99</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Charts/LSTP_Charts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803FEB36-CD08-43A3-9AFE-C9C7943B50EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C4DA68-21CF-4FC0-A539-16DCF8296940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EDE0999F-D750-4A98-AE9C-B65F0E79C2D3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="333">
   <si>
     <t>StepNo</t>
   </si>
@@ -212,27 +212,18 @@
     <t>Enter Home Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneHome</t>
-  </si>
-  <si>
     <t>TELEPHONEHOME</t>
   </si>
   <si>
     <t>Enter Mobile Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneMobile</t>
-  </si>
-  <si>
     <t>TELEPHONEMOBILE</t>
   </si>
   <si>
     <t>Enter Email address</t>
   </si>
   <si>
-    <t>txt_ TelephoneEmail</t>
-  </si>
-  <si>
     <t>EMAIL</t>
   </si>
   <si>
@@ -506,9 +497,6 @@
     <t>Select Intended Management</t>
   </si>
   <si>
-    <t>cmb_intended management</t>
-  </si>
-  <si>
     <t>INTENDED_MANAGEMENT</t>
   </si>
   <si>
@@ -545,9 +533,6 @@
     <t>Click Clinical Charts EPR tab to navigate to Clinical Charts section</t>
   </si>
   <si>
-    <t>btn_Clinical Charts</t>
-  </si>
-  <si>
     <t>Wait for Clinical Charts EPR tab to load</t>
   </si>
   <si>
@@ -1029,6 +1014,30 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>pageDefUsers</t>
+  </si>
+  <si>
+    <t>pageCreateNoteLORENZO</t>
+  </si>
+  <si>
+    <t>pageInitiateLORENZO</t>
+  </si>
+  <si>
+    <t>txt_TelephoneHome</t>
+  </si>
+  <si>
+    <t>txt_TelephoneMobile</t>
+  </si>
+  <si>
+    <t>txt_TelephoneEmail</t>
+  </si>
+  <si>
+    <t>cmb_intendedManagement</t>
+  </si>
+  <si>
+    <t>btn_ClinicalCharts</t>
   </si>
 </sst>
 </file>
@@ -1553,13 +1562,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -1607,7 +1616,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1644,7 +1653,7 @@
         <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1726,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
@@ -1757,7 +1766,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
@@ -1786,7 +1795,7 @@
         <v>30</v>
       </c>
       <c r="J20" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K20" t="s">
         <v>51</v>
@@ -1823,13 +1832,13 @@
         <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1837,19 +1846,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>329</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1857,19 +1866,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1877,13 +1886,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -1894,7 +1903,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
@@ -1908,19 +1917,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1928,19 +1937,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1948,19 +1957,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
         <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1968,19 +1977,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1988,19 +1997,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s">
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2008,19 +2017,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2028,16 +2037,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2045,10 +2054,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -2059,19 +2068,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="J35" t="s">
         <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" t="s">
-        <v>92</v>
-      </c>
-      <c r="J35" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2079,22 +2088,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" t="s">
         <v>94</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>91</v>
-      </c>
-      <c r="F36" t="s">
-        <v>95</v>
-      </c>
-      <c r="G36" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2102,16 +2111,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2119,7 +2128,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
@@ -2133,13 +2142,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -2150,7 +2159,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -2164,7 +2173,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -2215,13 +2224,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
         <v>22</v>
@@ -2232,10 +2241,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
@@ -2246,22 +2255,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" t="s">
         <v>110</v>
-      </c>
-      <c r="C46" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" t="s">
-        <v>111</v>
-      </c>
-      <c r="F46" t="s">
-        <v>95</v>
-      </c>
-      <c r="G46" t="s">
-        <v>112</v>
-      </c>
-      <c r="H46" t="s">
-        <v>113</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2272,19 +2281,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2292,10 +2301,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2306,13 +2315,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -2323,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -2337,13 +2346,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
@@ -2354,10 +2363,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -2368,19 +2377,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F53" t="s">
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2388,19 +2397,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F54" t="s">
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2408,19 +2417,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F55" t="s">
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2428,19 +2437,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F56" t="s">
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2448,13 +2457,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F57" t="s">
         <v>22</v>
@@ -2465,10 +2474,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -2479,22 +2488,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
         <v>48</v>
       </c>
       <c r="F59" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G59" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H59" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
@@ -2505,10 +2514,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2519,10 +2528,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
         <v>48</v>
@@ -2536,13 +2545,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F62" t="s">
         <v>22</v>
@@ -2553,10 +2562,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F63" t="s">
         <v>19</v>
@@ -2567,19 +2576,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F64" t="s">
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2587,19 +2596,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F65" t="s">
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2607,19 +2616,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D66" t="s">
-        <v>155</v>
+        <v>331</v>
       </c>
       <c r="F66" t="s">
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2627,19 +2636,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F67" t="s">
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2647,13 +2656,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
@@ -2664,10 +2673,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -2678,13 +2687,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -2695,10 +2704,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F71" t="s">
         <v>19</v>
@@ -2709,22 +2718,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" t="s">
+        <v>92</v>
+      </c>
+      <c r="G72" t="s">
         <v>109</v>
       </c>
-      <c r="D72" t="s">
-        <v>111</v>
-      </c>
-      <c r="F72" t="s">
-        <v>95</v>
-      </c>
-      <c r="G72" t="s">
-        <v>112</v>
-      </c>
       <c r="H72" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -2735,10 +2744,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F73" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2749,13 +2758,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>168</v>
+        <v>332</v>
       </c>
       <c r="F74" t="s">
         <v>22</v>
@@ -2766,10 +2775,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F75" t="s">
         <v>19</v>
@@ -2780,22 +2789,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C76" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" t="s">
+        <v>332</v>
+      </c>
+      <c r="F76" t="s">
+        <v>92</v>
+      </c>
+      <c r="G76" t="s">
         <v>109</v>
       </c>
-      <c r="D76" t="s">
-        <v>168</v>
-      </c>
-      <c r="F76" t="s">
-        <v>95</v>
-      </c>
-      <c r="G76" t="s">
-        <v>112</v>
-      </c>
       <c r="H76" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
@@ -2806,10 +2815,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F77" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2820,13 +2829,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F78" t="s">
         <v>22</v>
@@ -2837,10 +2846,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F79" t="s">
         <v>19</v>
@@ -2851,19 +2860,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F80" t="s">
         <v>30</v>
       </c>
       <c r="K80" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2871,13 +2880,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" t="s">
         <v>175</v>
-      </c>
-      <c r="D81" t="s">
-        <v>180</v>
       </c>
       <c r="F81" t="s">
         <v>22</v>
@@ -2888,10 +2897,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -2902,19 +2911,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F83" t="s">
         <v>30</v>
       </c>
       <c r="K83" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2922,10 +2931,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
@@ -2936,13 +2945,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C85" t="s">
+        <v>325</v>
+      </c>
+      <c r="D85" t="s">
         <v>182</v>
-      </c>
-      <c r="D85" t="s">
-        <v>187</v>
       </c>
       <c r="F85" t="s">
         <v>22</v>
@@ -2953,13 +2962,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C86" t="s">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c r="D86" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
         <v>22</v>
@@ -2970,10 +2979,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F87" t="s">
         <v>19</v>
@@ -2984,13 +2993,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D88" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F88" t="s">
         <v>22</v>
@@ -3001,10 +3010,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C89" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F89" t="s">
         <v>19</v>
@@ -3015,10 +3024,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F90" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3029,19 +3038,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C91" t="s">
+        <v>188</v>
+      </c>
+      <c r="D91" t="s">
+        <v>191</v>
+      </c>
+      <c r="E91" t="s">
+        <v>192</v>
+      </c>
+      <c r="F91" t="s">
         <v>193</v>
-      </c>
-      <c r="D91" t="s">
-        <v>196</v>
-      </c>
-      <c r="E91" t="s">
-        <v>197</v>
-      </c>
-      <c r="F91" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,10 +3058,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C92" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3063,16 +3072,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C93" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D93" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E93" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F93" t="s">
         <v>22</v>
@@ -3083,10 +3092,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C94" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3097,16 +3106,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C95" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E95" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F95" t="s">
         <v>22</v>
@@ -3117,10 +3126,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C96" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3131,16 +3140,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D97" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F97" t="s">
         <v>22</v>
@@ -3151,10 +3160,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C98" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -3165,13 +3174,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C99" t="s">
-        <v>210</v>
+        <v>326</v>
       </c>
       <c r="D99" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F99" t="s">
         <v>22</v>
@@ -3182,10 +3191,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C100" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -3196,25 +3205,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C101" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D101" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E101" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F101" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G101" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H101" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
@@ -3225,10 +3234,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3239,19 +3248,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C103" t="s">
+        <v>188</v>
+      </c>
+      <c r="D103" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" t="s">
+        <v>213</v>
+      </c>
+      <c r="F103" t="s">
         <v>193</v>
-      </c>
-      <c r="D103" t="s">
-        <v>217</v>
-      </c>
-      <c r="E103" t="s">
-        <v>218</v>
-      </c>
-      <c r="F103" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3259,10 +3268,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C104" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F104" t="s">
         <v>19</v>
@@ -3273,16 +3282,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C105" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D105" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E105" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
@@ -3293,10 +3302,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C106" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F106" t="s">
         <v>19</v>
@@ -3307,16 +3316,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D107" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E107" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F107" t="s">
         <v>22</v>
@@ -3327,10 +3336,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C108" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F108" t="s">
         <v>19</v>
@@ -3341,16 +3350,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C109" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D109" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E109" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F109" t="s">
         <v>22</v>
@@ -3361,10 +3370,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C110" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>19</v>
@@ -3375,13 +3384,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D111" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F111" t="s">
         <v>22</v>
@@ -3392,10 +3401,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C112" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F112" t="s">
         <v>19</v>
@@ -3406,25 +3415,25 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C113" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D113" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E113" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F113" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G113" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H113" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
@@ -3435,10 +3444,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F114" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -3449,19 +3458,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C115" t="s">
+        <v>188</v>
+      </c>
+      <c r="D115" t="s">
+        <v>231</v>
+      </c>
+      <c r="E115" t="s">
+        <v>232</v>
+      </c>
+      <c r="F115" t="s">
         <v>193</v>
-      </c>
-      <c r="D115" t="s">
-        <v>236</v>
-      </c>
-      <c r="E115" t="s">
-        <v>237</v>
-      </c>
-      <c r="F115" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -3469,10 +3478,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C116" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F116" t="s">
         <v>19</v>
@@ -3483,16 +3492,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C117" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D117" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E117" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F117" t="s">
         <v>22</v>
@@ -3503,10 +3512,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C118" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -3517,16 +3526,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C119" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D119" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E119" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
         <v>22</v>
@@ -3537,10 +3546,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C120" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F120" t="s">
         <v>19</v>
@@ -3551,16 +3560,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C121" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D121" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E121" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F121" t="s">
         <v>22</v>
@@ -3571,10 +3580,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C122" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3585,13 +3594,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C123" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="D123" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -3602,10 +3611,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C124" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -3616,25 +3625,25 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C125" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D125" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E125" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F125" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G125" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H125" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
@@ -3645,10 +3654,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F126" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -3659,13 +3668,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F127" t="s">
         <v>22</v>
@@ -3676,13 +3685,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F128" t="s">
         <v>22</v>
@@ -3693,7 +3702,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -3750,72 +3759,72 @@
         <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3824,52 +3833,52 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K2" t="s">
+        <v>261</v>
+      </c>
+      <c r="L2" t="s">
+        <v>262</v>
+      </c>
+      <c r="M2" t="s">
         <v>263</v>
       </c>
-      <c r="H2" t="s">
+      <c r="N2" t="s">
         <v>264</v>
       </c>
-      <c r="I2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>265</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>266</v>
       </c>
-      <c r="L2" t="s">
+      <c r="Q2" t="s">
         <v>267</v>
       </c>
-      <c r="M2" t="s">
+      <c r="R2" t="s">
         <v>268</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>269</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
         <v>270</v>
       </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
         <v>271</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="V2" t="s">
         <v>272</v>
-      </c>
-      <c r="R2" t="s">
-        <v>273</v>
-      </c>
-      <c r="S2" t="s">
-        <v>274</v>
-      </c>
-      <c r="T2" t="s">
-        <v>275</v>
-      </c>
-      <c r="U2" t="s">
-        <v>276</v>
-      </c>
-      <c r="V2" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3888,94 +3897,94 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3983,7 +3992,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3991,47 +4000,47 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4051,13 +4060,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,54 +4074,54 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
